--- a/حسابداری/بانک ها/ملت/1405/14050231-14050311.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14050231-14050311.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33600D11-6660-4B43-A1AF-05174DFCB4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D248613C-E07C-4D39-8E44-9707E1F27D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,23 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>کارمزد ۱ حواله سرجمع خرید شاپرک</t>
   </si>
   <si>
-    <t>اداره کل مدیریت عملیات</t>
-  </si>
-  <si>
-    <t>پذیرنده ۴۲۳۹۱۵۱</t>
-  </si>
-  <si>
-    <t>اداره امور پایا</t>
-  </si>
-  <si>
-    <t>اداره حسابداری متمرکز</t>
-  </si>
-  <si>
     <t>مانده</t>
   </si>
   <si>
@@ -57,18 +45,6 @@
     <t>واریز کننده/ ذیتفع</t>
   </si>
   <si>
-    <t>شماره سریال</t>
-  </si>
-  <si>
-    <t>شناسه واریز</t>
-  </si>
-  <si>
-    <t>کد حسابگری</t>
-  </si>
-  <si>
-    <t>شعبه</t>
-  </si>
-  <si>
     <t>زمان</t>
   </si>
   <si>
@@ -96,9 +72,6 @@
     <t>1405/02/31</t>
   </si>
   <si>
-    <t>حواله شاپرک ۰۵۰۲۳۰۰۳۱۱۰۰۰۰۰۰۰۰۴۲</t>
-  </si>
-  <si>
     <t>1405/03/04</t>
   </si>
   <si>
@@ -117,9 +90,6 @@
     <t>حواله همراه بانک بابت  ۹۳۰۴۶۷۳۵۹۴</t>
   </si>
   <si>
-    <t>اداره امور پرداخت لحظه ای</t>
-  </si>
-  <si>
     <t>IR۲۲۰۶۶۰۰۰۰۰۰۰۳۰۶۳۱۱۴۴۸۰۰۶</t>
   </si>
   <si>
@@ -127,25 +97,40 @@
   </si>
   <si>
     <t>قیمت ک</t>
+  </si>
+  <si>
+    <t>واریزی قاسم طالب</t>
+  </si>
+  <si>
+    <t>تمدید سایت شرکت</t>
+  </si>
+  <si>
+    <t>سرمیا گذاری روی نفت</t>
+  </si>
+  <si>
+    <t>ثبت شده برای دارایی شماره 1</t>
+  </si>
+  <si>
+    <t>1405/0327</t>
+  </si>
+  <si>
+    <t>10.000.000</t>
+  </si>
+  <si>
+    <t>پرداختی به سلفون معافی</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -155,18 +140,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -178,19 +161,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF57A16F"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDAECE1"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -204,17 +187,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -222,43 +205,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,310 +535,264 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="34.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="8.375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="28.625" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="4.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="48.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="25.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="10" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0.22421296296296298</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1200</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8">
+        <v>239350582</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="C3" s="3">
+        <v>0.56258101851851849</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="13">
+        <v>200000450</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>39350132</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="10">
+        <v>133</v>
+      </c>
+      <c r="M3" s="10">
+        <v>141</v>
+      </c>
+      <c r="N3" s="10">
+        <v>192</v>
+      </c>
+      <c r="O3" s="10">
+        <v>450</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3">
+        <v>9.3055555555555548E-3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="13">
+        <v>20370450</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>18979682</v>
+      </c>
+      <c r="I4" s="10">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="10">
+        <v>191</v>
+      </c>
+      <c r="M4" s="10">
+        <v>141</v>
+      </c>
+      <c r="N4" s="10">
+        <v>192</v>
+      </c>
+      <c r="O4" s="10">
+        <v>450</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.85172453703703699</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="10">
+        <v>660000000</v>
+      </c>
+      <c r="H5" s="4">
+        <v>678979682</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="10">
+        <v>60</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="15">
         <v>14</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1" s="9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.19012731481481482</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2">
-        <v>4481</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>2329735</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4">
-        <v>1100000</v>
-      </c>
-      <c r="L2" s="4">
-        <v>239351782</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-    </row>
-    <row r="3" spans="1:20" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="6">
-        <v>0.22421296296296298</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>1503</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>127947617</v>
-      </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11">
-        <v>1200</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>239350582</v>
-      </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-    </row>
-    <row r="4" spans="1:20" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.56258101851851849</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2402</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1579481115</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="12">
-        <v>200000450</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <v>39350132</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-    </row>
-    <row r="5" spans="1:20" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="6">
-        <v>9.3055555555555548E-3</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5">
-        <v>2402</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1582216100</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="11">
-        <v>20370450</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="7">
-        <v>18979682</v>
-      </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-    </row>
-    <row r="6" spans="1:20" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.85172453703703699</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="K19" s="14"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="2">
-        <v>82354</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>85580713</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4">
-        <v>660000000</v>
-      </c>
-      <c r="L6" s="4">
-        <v>678979682</v>
-      </c>
-      <c r="M6" s="4"/>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/حسابداری/بانک ها/ملت/1405/14050231-14050311.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14050231-14050311.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D248613C-E07C-4D39-8E44-9707E1F27D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78235D2-4B55-4F62-9407-2055BB43B057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -124,7 +135,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +165,13 @@
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -202,10 +224,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -231,9 +254,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -243,20 +263,33 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -543,9 +576,9 @@
     <col min="3" max="3" width="8.125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="48.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.25" style="18" customWidth="1"/>
     <col min="9" max="10" width="5.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.5" style="1" bestFit="1" customWidth="1"/>
@@ -558,52 +591,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -621,13 +654,13 @@
       <c r="E2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="15">
         <v>1200</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="15">
         <v>0</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="15">
         <v>239350582</v>
       </c>
       <c r="I2" s="8"/>
@@ -655,34 +688,34 @@
       <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="16">
         <v>200000450</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="17">
         <v>0</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="17">
         <v>39350132</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>133</v>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="9">
         <v>141</v>
       </c>
-      <c r="N3" s="10">
+      <c r="N3" s="9">
         <v>192</v>
       </c>
-      <c r="O3" s="10">
+      <c r="O3" s="9">
         <v>450</v>
       </c>
       <c r="P3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="11" t="s">
         <v>27</v>
       </c>
     </row>
@@ -702,30 +735,30 @@
       <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="16">
         <v>20370450</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="17">
         <v>0</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="17">
         <v>18979682</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>140</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>191</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>141</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9">
         <v>192</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="9">
         <v>450</v>
       </c>
       <c r="P4" s="4" t="s">
@@ -748,16 +781,16 @@
       <c r="E5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="10">
+      <c r="F5" s="17"/>
+      <c r="G5" s="16">
         <v>660000000</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="17">
         <v>678979682</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
-      <c r="K5" s="10">
+      <c r="K5" s="9">
         <v>60</v>
       </c>
       <c r="L5" s="4"/>
@@ -769,28 +802,28 @@
       </c>
     </row>
     <row r="19" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14" t="s">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="15">
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13">
         <v>14</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14" t="s">
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12" t="s">
         <v>30</v>
       </c>
     </row>
